--- a/esyluban/examples/dev/DataTables/test/define_from_excel.xlsx
+++ b/esyluban/examples/dev/DataTables/test/define_from_excel.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbDefineFromExcel2" &amp; value_type="DefineFromExcel2" &amp; read_schema_from_file="True" &amp; input="test/define_from_excel.xlsx" &amp; output="test_tbdefinefromexcel2"</t>
+          <t>full_name="test.TbDefineFromExcel2" &amp; read_schema_from_file="True" &amp; input="test/define_from_excel.xlsx"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/test/define_from_excel.xlsx
+++ b/esyluban/examples/dev/DataTables/test/define_from_excel.xlsx
@@ -1648,13 +1648,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="Z1:AB1"/>
     <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="R3:T3"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="W1:Y1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="W2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
